--- a/survey_templates/038_makeup_color_psychology_preference_survey--survey_templates.xlsx
+++ b/survey_templates/038_makeup_color_psychology_preference_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -761,7 +761,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C52"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
@@ -1146,17 +1146,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>preferred_mood_choices</t>
+          <t>favorite_season_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>adventurous</t>
+          <t>spring</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Adventurous</t>
+          <t>Spring</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>spring</t>
+          <t>summer</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Summer</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>summer</t>
+          <t>autumn</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Summer</t>
+          <t>Autumn</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>autumn</t>
+          <t>winter</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Autumn</t>
+          <t>Winter</t>
         </is>
       </c>
     </row>
@@ -1219,29 +1219,29 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>winter</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Winter</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>favorite_season_choices</t>
+          <t>color_preferred_for_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>face</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Face</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>face</t>
+          <t>skin</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Face</t>
+          <t>Skin</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>skin</t>
+          <t>hair</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Skin</t>
+          <t>Hair</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>hair</t>
+          <t>lips</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Hair</t>
+          <t>Lips</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>lips</t>
+          <t>eyes</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Lips</t>
+          <t>Eyes</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>eyes</t>
+          <t>eyebrows</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eyes</t>
+          <t>Eyebrows</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>eyebrows</t>
+          <t>eyelashes</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eyebrows</t>
+          <t>Eyelashes</t>
         </is>
       </c>
     </row>
@@ -1355,97 +1355,97 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>eyelashes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Eyelashes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>color_preferred_for_choices</t>
+          <t>preferred_color_shade_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>face</t>
+          <t>light</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Face</t>
+          <t>Light</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>color_preferred_for_choices</t>
+          <t>preferred_color_shade_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>hair</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hair</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>color_preferred_for_choices</t>
+          <t>preferred_color_shade_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>lips</t>
+          <t>dark</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lips</t>
+          <t>Dark</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>color_preferred_for_choices</t>
+          <t>preferred_color_shade_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>eyebrows</t>
+          <t>pastel</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Eyebrows</t>
+          <t>Pastel</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>color_preferred_for_choices</t>
+          <t>preferred_color_shade_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>bold</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Bold</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>light</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Light</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1474,180 +1474,95 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>preferred_color_shade_choices</t>
+          <t>preferred_mood_1_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>dark</t>
+          <t>happy</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Dark</t>
+          <t>Happy</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>preferred_color_shade_choices</t>
+          <t>preferred_mood_1_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>pastel</t>
+          <t>calm</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Pastel</t>
+          <t>Calm</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>preferred_color_shade_choices</t>
+          <t>preferred_mood_1_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>bold</t>
+          <t>confident</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bold</t>
+          <t>Confident</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>preferred_color_shade_choices</t>
+          <t>preferred_mood_1_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>neutral</t>
+          <t>energetic</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Neutral</t>
+          <t>Energetic</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>preferred_color_shade_choices</t>
+          <t>preferred_mood_1_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>relaxed</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>preferred_mood_1_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>happy</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Happy</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>preferred_mood_1_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>calm</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Calm</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>preferred_mood_1_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>confident</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Confident</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>preferred_mood_1_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>energetic</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Energetic</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>preferred_mood_1_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>relaxed</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
         <is>
           <t>Relaxed</t>
         </is>
